--- a/Hardware/Alert_Button_BOM.xlsx
+++ b/Hardware/Alert_Button_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thurs\Documents\Data Sheets\Alert Button\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2044CE-2CB3-40E3-A6AB-D34F206BA16F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3167E-7421-43CA-B26A-89D087A9B83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="0" windowWidth="26490" windowHeight="15585" xr2:uid="{DEE8CDB2-58AA-416D-8F4E-F1210A55A9A6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DEE8CDB2-58AA-416D-8F4E-F1210A55A9A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Alert_Button_BOM" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="115">
   <si>
     <t>Comment</t>
   </si>
@@ -375,6 +375,15 @@
   </si>
   <si>
     <t>CN1, CN2</t>
+  </si>
+  <si>
+    <t>NTCG103JX103DTDS</t>
+  </si>
+  <si>
+    <t>RT1</t>
+  </si>
+  <si>
+    <t>NTC Thermistor</t>
   </si>
 </sst>
 </file>
@@ -804,7 +813,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.5703125" customWidth="1"/>
@@ -1440,59 +1449,59 @@
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>85</v>
       </c>
       <c r="C34" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>102</v>
@@ -1500,19 +1509,19 @@
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>102</v>
@@ -1520,67 +1529,87 @@
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4">
         <v>1</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C39" s="4">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="42" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.30555555555555558" bottom="0.30555555555555558" header="0" footer="0"/>

--- a/Hardware/Alert_Button_BOM.xlsx
+++ b/Hardware/Alert_Button_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thurs\Documents\Data Sheets\Alert Button\Hardware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB3167E-7421-43CA-B26A-89D087A9B83D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1C6E5E-E8C6-431C-9A8A-CA537BE99062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DEE8CDB2-58AA-416D-8F4E-F1210A55A9A6}"/>
   </bookViews>
@@ -263,9 +263,6 @@
     <t>R2, R5, R8</t>
   </si>
   <si>
-    <t>40k</t>
-  </si>
-  <si>
     <t>R3, R6</t>
   </si>
   <si>
@@ -384,6 +381,9 @@
   </si>
   <si>
     <t>NTC Thermistor</t>
+  </si>
+  <si>
+    <t>20k</t>
   </si>
 </sst>
 </file>
@@ -844,7 +844,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -862,7 +862,7 @@
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -882,7 +882,7 @@
         <v>10</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -902,7 +902,7 @@
         <v>10</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -920,7 +920,7 @@
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -940,7 +940,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -960,7 +960,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -980,7 +980,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -998,7 +998,7 @@
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>30</v>
@@ -1066,13 +1066,13 @@
         <v>2</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1100,7 +1100,7 @@
         <v>36</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C15" s="4">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>36</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1120,7 +1120,7 @@
         <v>38</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C16" s="4">
         <v>1</v>
@@ -1132,7 +1132,7 @@
         <v>38</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1152,7 +1152,7 @@
         <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1172,7 +1172,7 @@
         <v>43</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1192,7 +1192,7 @@
         <v>46</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
         <v>49</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1232,7 +1232,7 @@
         <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1252,7 +1252,7 @@
         <v>57</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1272,7 +1272,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1292,7 +1292,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1312,7 +1312,7 @@
         <v>66</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1350,12 +1350,12 @@
         <v>10</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>70</v>
@@ -1364,18 +1364,18 @@
         <v>2</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>70</v>
@@ -1384,16 +1384,16 @@
         <v>1</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>70</v>
@@ -1402,16 +1402,16 @@
         <v>1</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>70</v>
@@ -1420,18 +1420,18 @@
         <v>4</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>70</v>
@@ -1440,171 +1440,171 @@
         <v>1</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="4">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="4">
-        <v>1</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="E33" s="8" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F33" s="8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="4">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C34" s="4">
-        <v>1</v>
-      </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="4">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C36" s="4">
-        <v>1</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C37" s="4">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C37" s="4">
-        <v>1</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="4">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C38" s="4">
-        <v>1</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C39" s="4">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C39" s="4">
-        <v>1</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="4">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="4">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
